--- a/tools/import-cli/templates/TEMPLATE_KOSONG.xlsx
+++ b/tools/import-cli/templates/TEMPLATE_KOSONG.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="38">
   <si>
     <t>nama_kategori</t>
   </si>
@@ -85,6 +85,18 @@
   </si>
   <si>
     <t>stok_minimum</t>
+  </si>
+  <si>
+    <t>satuan_besar</t>
+  </si>
+  <si>
+    <t>isi</t>
+  </si>
+  <si>
+    <t>harga_satuan_besar</t>
+  </si>
+  <si>
+    <t>barcode_satuan_besar</t>
   </si>
   <si>
     <t>kode_produk_induk</t>
@@ -799,7 +811,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N201"/>
+  <dimension ref="A1:R201"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -813,9 +825,13 @@
     <col min="12" max="12" width="13" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="16" max="16" width="8" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -857,6 +873,18 @@
       </c>
       <c r="N1" s="2" t="s">
         <v>22</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="3:13" x14ac:dyDescent="0.25"/>
@@ -1104,13 +1132,13 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>14</v>
@@ -1125,16 +1153,16 @@
         <v>18</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25"/>
@@ -1382,13 +1410,13 @@
         <v>3</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25"/>
@@ -1624,10 +1652,10 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>8</v>
